--- a/artfynd/A 54940-2025 artfynd.xlsx
+++ b/artfynd/A 54940-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129974105</v>
       </c>
       <c r="B2" t="n">
-        <v>100983</v>
+        <v>100986</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>129974179</v>
       </c>
       <c r="B3" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>129974211</v>
       </c>
       <c r="B4" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
         <v>129974131</v>
       </c>
       <c r="B5" t="n">
-        <v>91602</v>
+        <v>91605</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1156,7 +1156,7 @@
         <v>129974181</v>
       </c>
       <c r="B6" t="n">
-        <v>100983</v>
+        <v>100986</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 54940-2025 artfynd.xlsx
+++ b/artfynd/A 54940-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129974105</v>
       </c>
       <c r="B2" t="n">
-        <v>100986</v>
+        <v>100987</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>129974179</v>
       </c>
       <c r="B3" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>129974211</v>
       </c>
       <c r="B4" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
         <v>129974131</v>
       </c>
       <c r="B5" t="n">
-        <v>91605</v>
+        <v>91606</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1156,7 +1156,7 @@
         <v>129974181</v>
       </c>
       <c r="B6" t="n">
-        <v>100986</v>
+        <v>100987</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 54940-2025 artfynd.xlsx
+++ b/artfynd/A 54940-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129974105</v>
       </c>
       <c r="B2" t="n">
-        <v>100987</v>
+        <v>101004</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>129974179</v>
       </c>
       <c r="B3" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>129974211</v>
       </c>
       <c r="B4" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
         <v>129974131</v>
       </c>
       <c r="B5" t="n">
-        <v>91606</v>
+        <v>91623</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1156,7 +1156,7 @@
         <v>129974181</v>
       </c>
       <c r="B6" t="n">
-        <v>100987</v>
+        <v>101004</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 54940-2025 artfynd.xlsx
+++ b/artfynd/A 54940-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129974105</v>
       </c>
       <c r="B2" t="n">
-        <v>101020</v>
+        <v>101022</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>129974179</v>
       </c>
       <c r="B3" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>129974211</v>
       </c>
       <c r="B4" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
         <v>129974131</v>
       </c>
       <c r="B5" t="n">
-        <v>91639</v>
+        <v>91641</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1156,7 +1156,7 @@
         <v>129974181</v>
       </c>
       <c r="B6" t="n">
-        <v>101020</v>
+        <v>101022</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 54940-2025 artfynd.xlsx
+++ b/artfynd/A 54940-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129974105</v>
       </c>
       <c r="B2" t="n">
-        <v>101022</v>
+        <v>101109</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>129974179</v>
       </c>
       <c r="B3" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>129974211</v>
       </c>
       <c r="B4" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
         <v>129974131</v>
       </c>
       <c r="B5" t="n">
-        <v>91641</v>
+        <v>91728</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1156,7 +1156,7 @@
         <v>129974181</v>
       </c>
       <c r="B6" t="n">
-        <v>101022</v>
+        <v>101109</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 54940-2025 artfynd.xlsx
+++ b/artfynd/A 54940-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,38 +675,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129974105</v>
+        <v>129974131</v>
       </c>
       <c r="B2" t="n">
-        <v>101109</v>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -714,13 +713,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>516331</v>
+        <v>516319</v>
       </c>
       <c r="R2" t="n">
-        <v>6668692</v>
+        <v>6668661</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -769,7 +768,22 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>inslag av gamla tallar</t>
+          <t>Inslag av gamla tallar. Kalkmarksskog. Avverkningsplanerat.</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>granlåga i liten bröte # Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -787,57 +801,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129974179</v>
+        <v>96603593</v>
       </c>
       <c r="B3" t="n">
-        <v>98920</v>
+        <v>91680</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>3215</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Skarviksberget, Dlr</t>
+          <t>Limnäsudden - Skarvikberget, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>516259</v>
+        <v>516225</v>
       </c>
       <c r="R3" t="n">
-        <v>6668701</v>
+        <v>6668675</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -864,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2021-10-11</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2021-10-11</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,12 +889,12 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>Lågörtgranskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Inslag av gamla tallar. Kalkmarksskog. Avverkningsplanerat.</t>
+          <t>kalkmarksskog</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -907,57 +912,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129974211</v>
+        <v>96603589</v>
       </c>
       <c r="B4" t="n">
-        <v>98920</v>
+        <v>92869</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>4769</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Skarviksberget, Dlr</t>
+          <t>Limnäsudden - Skarvikberget, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>516279</v>
+        <v>516225</v>
       </c>
       <c r="R4" t="n">
-        <v>6668684</v>
+        <v>6668675</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -984,12 +980,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2021-10-11</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2021-10-11</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1004,12 +1000,12 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>Lågörtgranskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Inslag av gamla tallar. Kalkmarksskog. Avverkningsplanerat.</t>
+          <t>kalkmarksskog</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1027,32 +1023,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129974131</v>
+        <v>129974173</v>
       </c>
       <c r="B5" t="n">
-        <v>91728</v>
+        <v>92869</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>4769</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1065,10 +1061,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>516319</v>
+        <v>516220</v>
       </c>
       <c r="R5" t="n">
-        <v>6668661</v>
+        <v>6668664</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1135,7 +1131,7 @@
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>granlåga i liten bröte # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1153,10 +1149,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129974181</v>
+        <v>129974143</v>
       </c>
       <c r="B6" t="n">
-        <v>101109</v>
+        <v>91282</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1164,27 +1160,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222498</v>
+        <v>5685</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1192,10 +1187,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>516284</v>
+        <v>516272</v>
       </c>
       <c r="R6" t="n">
-        <v>6668713</v>
+        <v>6668613</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1250,6 +1245,21 @@
           <t>Inslag av gamla tallar. Kalkmarksskog. Avverkningsplanerat.</t>
         </is>
       </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>tallåga bland gamla granlågor # Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
@@ -1262,6 +1272,806 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>129974179</v>
+      </c>
+      <c r="B7" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Skarviksberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>516259</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6668701</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Norrbärke</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Inslag av gamla tallar. Kalkmarksskog. Avverkningsplanerat.</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>129974211</v>
+      </c>
+      <c r="B8" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Skarviksberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>516279</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6668684</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Norrbärke</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Inslag av gamla tallar. Kalkmarksskog. Avverkningsplanerat.</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>96603576</v>
+      </c>
+      <c r="B9" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Limnäsudden - Skarvikberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>516225</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6668675</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Norrbärke</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2021-10-11</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2021-10-11</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>kalkmarksskog</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>129974105</v>
+      </c>
+      <c r="B10" t="n">
+        <v>101325</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Skarviksberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>516331</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6668692</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Norrbärke</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>inslag av gamla tallar</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>129974151</v>
+      </c>
+      <c r="B11" t="n">
+        <v>101325</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Skarviksberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>516214</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6668657</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Norrbärke</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Inslag av gamla tallar. Kalkmarksskog. Avverkningsplanerat.</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>129974181</v>
+      </c>
+      <c r="B12" t="n">
+        <v>101325</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Skarviksberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>516284</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6668713</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Norrbärke</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Inslag av gamla tallar. Kalkmarksskog. Avverkningsplanerat.</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>129974196</v>
+      </c>
+      <c r="B13" t="n">
+        <v>101325</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Skarviksberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>516330</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6668614</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Norrbärke</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>Inslag av gamla tallar. Kalkmarksskog. Avverkningsplanerat.</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 54940-2025 artfynd.xlsx
+++ b/artfynd/A 54940-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AZ13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -798,6 +803,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129974131</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -909,6 +919,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96603593</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1020,6 +1035,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96603589</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1146,6 +1166,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129974173</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1272,6 +1297,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129974143</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1392,6 +1422,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129974179</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1512,6 +1547,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129974211</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1624,6 +1664,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96603576</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1736,6 +1781,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129974105</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1848,6 +1898,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129974151</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1960,6 +2015,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129974181</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2072,8 +2132,27 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129974196</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 54940-2025 artfynd.xlsx
+++ b/artfynd/A 54940-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ13"/>
+  <dimension ref="A1:AZ22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -811,10 +811,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>96603593</v>
+        <v>135775340</v>
       </c>
       <c r="B3" t="n">
-        <v>91680</v>
+        <v>96486</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -822,37 +822,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3215</v>
+        <v>2812</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Limnäsudden - Skarvikberget, Dlr</t>
+          <t>Limnäsudden, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>516225</v>
+        <v>516356</v>
       </c>
       <c r="R3" t="n">
-        <v>6668675</v>
+        <v>6668771</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -879,12 +876,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2021-10-11</t>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2021-10-11</t>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -893,44 +900,33 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>kalkmarksskog</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96603593</t>
+          <t>https://artportalen.se/Sighting/135775340</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>96603589</v>
+        <v>96603593</v>
       </c>
       <c r="B4" t="n">
-        <v>92869</v>
+        <v>91680</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -938,21 +934,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4769</v>
+        <v>3215</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -1037,13 +1033,13 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96603589</t>
+          <t>https://artportalen.se/Sighting/96603593</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129974173</v>
+        <v>96603589</v>
       </c>
       <c r="B5" t="n">
         <v>92869</v>
@@ -1077,14 +1073,14 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Skarviksberget, Dlr</t>
+          <t>Limnäsudden - Skarvikberget, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>516220</v>
+        <v>516225</v>
       </c>
       <c r="R5" t="n">
-        <v>6668664</v>
+        <v>6668675</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1111,12 +1107,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2021-10-11</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2021-10-11</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1131,27 +1127,12 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>Lågörtgranskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Inslag av gamla tallar. Kalkmarksskog. Avverkningsplanerat.</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+          <t>kalkmarksskog</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1168,16 +1149,16 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129974173</t>
+          <t>https://artportalen.se/Sighting/96603589</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129974143</v>
+        <v>129974173</v>
       </c>
       <c r="B6" t="n">
-        <v>91282</v>
+        <v>92869</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1185,21 +1166,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5685</v>
+        <v>4769</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1212,10 +1193,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>516272</v>
+        <v>516220</v>
       </c>
       <c r="R6" t="n">
-        <v>6668613</v>
+        <v>6668664</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1272,17 +1253,17 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>tallåga bland gamla granlågor # Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1299,52 +1280,43 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129974143</t>
+          <t>https://artportalen.se/Sighting/129974173</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129974179</v>
+        <v>129974143</v>
       </c>
       <c r="B7" t="n">
-        <v>99118</v>
+        <v>91282</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>5685</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Fr.) Jülich</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1352,10 +1324,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>516259</v>
+        <v>516272</v>
       </c>
       <c r="R7" t="n">
-        <v>6668701</v>
+        <v>6668613</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1410,6 +1382,21 @@
           <t>Inslag av gamla tallar. Kalkmarksskog. Avverkningsplanerat.</t>
         </is>
       </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>tallåga bland gamla granlågor # Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
@@ -1424,63 +1411,51 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129974179</t>
+          <t>https://artportalen.se/Sighting/129974143</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129974211</v>
+        <v>135775349</v>
       </c>
       <c r="B8" t="n">
-        <v>99118</v>
+        <v>4776</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>100299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Skarviksberget, Dlr</t>
+          <t>Limnäsudden, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>516279</v>
+        <v>516333</v>
       </c>
       <c r="R8" t="n">
-        <v>6668684</v>
+        <v>6668702</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1507,12 +1482,27 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>17:05</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Stående död gran, lågörtgranskog</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1521,83 +1511,80 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>Lågörtgranskog</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>Inslag av gamla tallar. Kalkmarksskog. Avverkningsplanerat.</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129974211</t>
+          <t>https://artportalen.se/Sighting/135775349</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>96603576</v>
+        <v>129974179</v>
       </c>
       <c r="B9" t="n">
-        <v>101326</v>
+        <v>99118</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Limnäsudden - Skarvikberget, Dlr</t>
+          <t>Skarviksberget, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>516225</v>
+        <v>516259</v>
       </c>
       <c r="R9" t="n">
-        <v>6668675</v>
+        <v>6668701</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1624,12 +1611,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2021-10-11</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2021-10-11</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1644,12 +1631,12 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Lågörtgranskog</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>kalkmarksskog</t>
+          <t>Inslag av gamla tallar. Kalkmarksskog. Avverkningsplanerat.</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1666,42 +1653,50 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96603576</t>
+          <t>https://artportalen.se/Sighting/129974179</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129974105</v>
+        <v>129974211</v>
       </c>
       <c r="B10" t="n">
-        <v>101325</v>
+        <v>99118</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
@@ -1711,13 +1706,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>516331</v>
+        <v>516279</v>
       </c>
       <c r="R10" t="n">
-        <v>6668692</v>
+        <v>6668684</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1766,7 +1761,7 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>inslag av gamla tallar</t>
+          <t>Inslag av gamla tallar. Kalkmarksskog. Avverkningsplanerat.</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1783,16 +1778,16 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129974105</t>
+          <t>https://artportalen.se/Sighting/129974211</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129974151</v>
+        <v>96603576</v>
       </c>
       <c r="B11" t="n">
-        <v>101325</v>
+        <v>101326</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1824,14 +1819,14 @@
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Skarviksberget, Dlr</t>
+          <t>Limnäsudden - Skarvikberget, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>516214</v>
+        <v>516225</v>
       </c>
       <c r="R11" t="n">
-        <v>6668657</v>
+        <v>6668675</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1858,12 +1853,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2021-10-11</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2021-10-11</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1878,12 +1873,12 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>Lågörtgranskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Inslag av gamla tallar. Kalkmarksskog. Avverkningsplanerat.</t>
+          <t>kalkmarksskog</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1900,13 +1895,13 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129974151</t>
+          <t>https://artportalen.se/Sighting/96603576</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129974181</v>
+        <v>129974105</v>
       </c>
       <c r="B12" t="n">
         <v>101325</v>
@@ -1945,13 +1940,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>516284</v>
+        <v>516331</v>
       </c>
       <c r="R12" t="n">
-        <v>6668713</v>
+        <v>6668692</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2000,7 +1995,7 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Inslag av gamla tallar. Kalkmarksskog. Avverkningsplanerat.</t>
+          <t>inslag av gamla tallar</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2017,13 +2012,13 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129974181</t>
+          <t>https://artportalen.se/Sighting/129974105</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129974196</v>
+        <v>129974151</v>
       </c>
       <c r="B13" t="n">
         <v>101325</v>
@@ -2062,10 +2057,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>516330</v>
+        <v>516214</v>
       </c>
       <c r="R13" t="n">
-        <v>6668614</v>
+        <v>6668657</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2134,7 +2129,1035 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/129974151</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>129974181</v>
+      </c>
+      <c r="B14" t="n">
+        <v>101325</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Skarviksberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>516284</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6668713</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Norrbärke</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>Inslag av gamla tallar. Kalkmarksskog. Avverkningsplanerat.</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129974181</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>129974196</v>
+      </c>
+      <c r="B15" t="n">
+        <v>101325</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Skarviksberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>516330</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6668614</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Norrbärke</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>Inslag av gamla tallar. Kalkmarksskog. Avverkningsplanerat.</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/129974196</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>135775337</v>
+      </c>
+      <c r="B16" t="n">
+        <v>101483</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Limnäsudden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>516387</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6668808</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Norrbärke</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>16:50</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>16:50</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135775337</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>135775341</v>
+      </c>
+      <c r="B17" t="n">
+        <v>101483</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Limnäsudden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>516353</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6668765</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Norrbärke</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>16:54</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>16:54</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135775341</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>135775344</v>
+      </c>
+      <c r="B18" t="n">
+        <v>101483</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Limnäsudden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>516325</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6668756</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Norrbärke</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>16:58</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>16:58</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135775344</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>135775346</v>
+      </c>
+      <c r="B19" t="n">
+        <v>101483</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Limnäsudden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>516325</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6668729</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Norrbärke</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>16:59</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>16:59</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135775346</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>135775350</v>
+      </c>
+      <c r="B20" t="n">
+        <v>101483</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Limnäsudden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>516342</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6668692</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Norrbärke</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>17:06</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>17:06</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135775350</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>135775354</v>
+      </c>
+      <c r="B21" t="n">
+        <v>101483</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Limnäsudden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>516349</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6668748</v>
+      </c>
+      <c r="S21" t="n">
+        <v>8</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Norrbärke</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135775354</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>135775355</v>
+      </c>
+      <c r="B22" t="n">
+        <v>99080</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>223049</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Ormbär</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Paris quadrifolia</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Limnäsudden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>516339</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6668746</v>
+      </c>
+      <c r="S22" t="n">
+        <v>12</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Norrbärke</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>17:24</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>17:24</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135775355</t>
         </is>
       </c>
     </row>
@@ -2152,6 +3175,15 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 54940-2025 artfynd.xlsx
+++ b/artfynd/A 54940-2025 artfynd.xlsx
@@ -814,7 +814,7 @@
         <v>135775340</v>
       </c>
       <c r="B3" t="n">
-        <v>96486</v>
+        <v>96488</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -2372,7 +2372,7 @@
         <v>135775337</v>
       </c>
       <c r="B16" t="n">
-        <v>101483</v>
+        <v>101485</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2484,7 +2484,7 @@
         <v>135775341</v>
       </c>
       <c r="B17" t="n">
-        <v>101483</v>
+        <v>101485</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2596,7 +2596,7 @@
         <v>135775344</v>
       </c>
       <c r="B18" t="n">
-        <v>101483</v>
+        <v>101485</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2713,7 +2713,7 @@
         <v>135775346</v>
       </c>
       <c r="B19" t="n">
-        <v>101483</v>
+        <v>101485</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2830,7 +2830,7 @@
         <v>135775350</v>
       </c>
       <c r="B20" t="n">
-        <v>101483</v>
+        <v>101485</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2942,7 +2942,7 @@
         <v>135775354</v>
       </c>
       <c r="B21" t="n">
-        <v>101483</v>
+        <v>101485</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3054,7 +3054,7 @@
         <v>135775355</v>
       </c>
       <c r="B22" t="n">
-        <v>99080</v>
+        <v>99082</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 54940-2025 artfynd.xlsx
+++ b/artfynd/A 54940-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ22"/>
+  <dimension ref="A1:AZ13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -811,10 +811,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>135775340</v>
+        <v>96603593</v>
       </c>
       <c r="B3" t="n">
-        <v>96488</v>
+        <v>91680</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -822,34 +822,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2812</v>
+        <v>3215</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kransmossa</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hylocomiadelphus triquetrus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Ochyra &amp; Stebel</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Limnäsudden, Dlr</t>
+          <t>Limnäsudden - Skarvikberget, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>516356</v>
+        <v>516225</v>
       </c>
       <c r="R3" t="n">
-        <v>6668771</v>
+        <v>6668675</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -876,22 +879,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>16:54</t>
+          <t>2021-10-11</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>16:54</t>
+          <t>2021-10-11</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -900,33 +893,44 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>kalkmarksskog</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135775340</t>
+          <t>https://artportalen.se/Sighting/96603593</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>96603593</v>
+        <v>96603589</v>
       </c>
       <c r="B4" t="n">
-        <v>91680</v>
+        <v>92869</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -934,21 +938,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3215</v>
+        <v>4769</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -1033,13 +1037,13 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96603593</t>
+          <t>https://artportalen.se/Sighting/96603589</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>96603589</v>
+        <v>129974173</v>
       </c>
       <c r="B5" t="n">
         <v>92869</v>
@@ -1073,14 +1077,14 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Limnäsudden - Skarvikberget, Dlr</t>
+          <t>Skarviksberget, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>516225</v>
+        <v>516220</v>
       </c>
       <c r="R5" t="n">
-        <v>6668675</v>
+        <v>6668664</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1107,12 +1111,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2021-10-11</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2021-10-11</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1127,12 +1131,27 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Lågörtgranskog</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>kalkmarksskog</t>
+          <t>Inslag av gamla tallar. Kalkmarksskog. Avverkningsplanerat.</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1149,16 +1168,16 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96603589</t>
+          <t>https://artportalen.se/Sighting/129974173</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129974173</v>
+        <v>129974143</v>
       </c>
       <c r="B6" t="n">
-        <v>92869</v>
+        <v>91282</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1166,21 +1185,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4769</v>
+        <v>5685</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1193,10 +1212,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>516220</v>
+        <v>516272</v>
       </c>
       <c r="R6" t="n">
-        <v>6668664</v>
+        <v>6668613</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1253,17 +1272,17 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>tallåga bland gamla granlågor # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1280,43 +1299,52 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129974173</t>
+          <t>https://artportalen.se/Sighting/129974143</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129974143</v>
+        <v>129974179</v>
       </c>
       <c r="B7" t="n">
-        <v>91282</v>
+        <v>99118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5685</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1324,10 +1352,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>516272</v>
+        <v>516259</v>
       </c>
       <c r="R7" t="n">
-        <v>6668613</v>
+        <v>6668701</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1382,21 +1410,6 @@
           <t>Inslag av gamla tallar. Kalkmarksskog. Avverkningsplanerat.</t>
         </is>
       </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>tallåga bland gamla granlågor # Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
@@ -1411,51 +1424,63 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129974143</t>
+          <t>https://artportalen.se/Sighting/129974179</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>135775349</v>
+        <v>129974211</v>
       </c>
       <c r="B8" t="n">
-        <v>4776</v>
+        <v>99118</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100299</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Limnäsudden, Dlr</t>
+          <t>Skarviksberget, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>516333</v>
+        <v>516279</v>
       </c>
       <c r="R8" t="n">
-        <v>6668702</v>
+        <v>6668684</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1482,27 +1507,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>17:05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>17:05</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Stående död gran, lågörtgranskog</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1511,80 +1521,83 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Inslag av gamla tallar. Kalkmarksskog. Avverkningsplanerat.</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135775349</t>
+          <t>https://artportalen.se/Sighting/129974211</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129974179</v>
+        <v>96603576</v>
       </c>
       <c r="B9" t="n">
-        <v>99118</v>
+        <v>101326</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Skarviksberget, Dlr</t>
+          <t>Limnäsudden - Skarvikberget, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>516259</v>
+        <v>516225</v>
       </c>
       <c r="R9" t="n">
-        <v>6668701</v>
+        <v>6668675</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1611,12 +1624,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2021-10-11</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2021-10-11</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1631,12 +1644,12 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>Lågörtgranskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Inslag av gamla tallar. Kalkmarksskog. Avverkningsplanerat.</t>
+          <t>kalkmarksskog</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1653,50 +1666,42 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129974179</t>
+          <t>https://artportalen.se/Sighting/96603576</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129974211</v>
+        <v>129974105</v>
       </c>
       <c r="B10" t="n">
-        <v>99118</v>
+        <v>101325</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
@@ -1706,13 +1711,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>516279</v>
+        <v>516331</v>
       </c>
       <c r="R10" t="n">
-        <v>6668684</v>
+        <v>6668692</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1761,7 +1766,7 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Inslag av gamla tallar. Kalkmarksskog. Avverkningsplanerat.</t>
+          <t>inslag av gamla tallar</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1778,16 +1783,16 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129974211</t>
+          <t>https://artportalen.se/Sighting/129974105</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>96603576</v>
+        <v>129974151</v>
       </c>
       <c r="B11" t="n">
-        <v>101326</v>
+        <v>101325</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1819,14 +1824,14 @@
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Limnäsudden - Skarvikberget, Dlr</t>
+          <t>Skarviksberget, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>516225</v>
+        <v>516214</v>
       </c>
       <c r="R11" t="n">
-        <v>6668675</v>
+        <v>6668657</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1853,12 +1858,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2021-10-11</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2021-10-11</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1873,12 +1878,12 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Lågörtgranskog</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>kalkmarksskog</t>
+          <t>Inslag av gamla tallar. Kalkmarksskog. Avverkningsplanerat.</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1895,13 +1900,13 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96603576</t>
+          <t>https://artportalen.se/Sighting/129974151</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129974105</v>
+        <v>129974181</v>
       </c>
       <c r="B12" t="n">
         <v>101325</v>
@@ -1940,13 +1945,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>516331</v>
+        <v>516284</v>
       </c>
       <c r="R12" t="n">
-        <v>6668692</v>
+        <v>6668713</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1995,7 +2000,7 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>inslag av gamla tallar</t>
+          <t>Inslag av gamla tallar. Kalkmarksskog. Avverkningsplanerat.</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2012,13 +2017,13 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129974105</t>
+          <t>https://artportalen.se/Sighting/129974181</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129974151</v>
+        <v>129974196</v>
       </c>
       <c r="B13" t="n">
         <v>101325</v>
@@ -2057,10 +2062,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>516214</v>
+        <v>516330</v>
       </c>
       <c r="R13" t="n">
-        <v>6668657</v>
+        <v>6668614</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2129,1035 +2134,7 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129974151</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>129974181</v>
-      </c>
-      <c r="B14" t="n">
-        <v>101325</v>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>222498</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Blåsippa</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>Hepatica nobilis</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>Skarviksberget, Dlr</t>
-        </is>
-      </c>
-      <c r="Q14" t="n">
-        <v>516284</v>
-      </c>
-      <c r="R14" t="n">
-        <v>6668713</v>
-      </c>
-      <c r="S14" t="n">
-        <v>5</v>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>Smedjebacken</t>
-        </is>
-      </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>Norrbärke</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>2025-12-04</t>
-        </is>
-      </c>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t>2025-12-04</t>
-        </is>
-      </c>
-      <c r="AD14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF14" t="inlineStr"/>
-      <c r="AG14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>Lågörtgranskog</t>
-        </is>
-      </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>Inslag av gamla tallar. Kalkmarksskog. Avverkningsplanerat.</t>
-        </is>
-      </c>
-      <c r="AT14" t="inlineStr"/>
-      <c r="AW14" t="inlineStr">
-        <is>
-          <t>Janolof Hermansson</t>
-        </is>
-      </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>Janolof Hermansson</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr"/>
-      <c r="AZ14" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/129974181</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>129974196</v>
-      </c>
-      <c r="B15" t="n">
-        <v>101325</v>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>222498</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Blåsippa</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Hepatica nobilis</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>Skarviksberget, Dlr</t>
-        </is>
-      </c>
-      <c r="Q15" t="n">
-        <v>516330</v>
-      </c>
-      <c r="R15" t="n">
-        <v>6668614</v>
-      </c>
-      <c r="S15" t="n">
-        <v>5</v>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>Smedjebacken</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>Norrbärke</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>2025-12-04</t>
-        </is>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>2025-12-04</t>
-        </is>
-      </c>
-      <c r="AD15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF15" t="inlineStr"/>
-      <c r="AG15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>Lågörtgranskog</t>
-        </is>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>Inslag av gamla tallar. Kalkmarksskog. Avverkningsplanerat.</t>
-        </is>
-      </c>
-      <c r="AT15" t="inlineStr"/>
-      <c r="AW15" t="inlineStr">
-        <is>
-          <t>Janolof Hermansson</t>
-        </is>
-      </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>Janolof Hermansson</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr"/>
-      <c r="AZ15" t="inlineStr">
-        <is>
           <t>https://artportalen.se/Sighting/129974196</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>135775337</v>
-      </c>
-      <c r="B16" t="n">
-        <v>101485</v>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>222498</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Blåsippa</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>Hepatica nobilis</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>Limnäsudden, Dlr</t>
-        </is>
-      </c>
-      <c r="Q16" t="n">
-        <v>516387</v>
-      </c>
-      <c r="R16" t="n">
-        <v>6668808</v>
-      </c>
-      <c r="S16" t="n">
-        <v>5</v>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>Smedjebacken</t>
-        </is>
-      </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>Norrbärke</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>2026-08-09</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>16:50</t>
-        </is>
-      </c>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>2026-08-09</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>16:50</t>
-        </is>
-      </c>
-      <c r="AD16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT16" t="inlineStr"/>
-      <c r="AW16" t="inlineStr">
-        <is>
-          <t>Alec Bailey</t>
-        </is>
-      </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>Alec Bailey</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr"/>
-      <c r="AZ16" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135775337</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>135775341</v>
-      </c>
-      <c r="B17" t="n">
-        <v>101485</v>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>222498</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Blåsippa</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Hepatica nobilis</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>Limnäsudden, Dlr</t>
-        </is>
-      </c>
-      <c r="Q17" t="n">
-        <v>516353</v>
-      </c>
-      <c r="R17" t="n">
-        <v>6668765</v>
-      </c>
-      <c r="S17" t="n">
-        <v>5</v>
-      </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>Smedjebacken</t>
-        </is>
-      </c>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>Norrbärke</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>2026-08-09</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>16:54</t>
-        </is>
-      </c>
-      <c r="AA17" t="inlineStr">
-        <is>
-          <t>2026-08-09</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>16:54</t>
-        </is>
-      </c>
-      <c r="AD17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT17" t="inlineStr"/>
-      <c r="AW17" t="inlineStr">
-        <is>
-          <t>Alec Bailey</t>
-        </is>
-      </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>Alec Bailey</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr"/>
-      <c r="AZ17" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135775341</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>135775344</v>
-      </c>
-      <c r="B18" t="n">
-        <v>101485</v>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>222498</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Blåsippa</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>Hepatica nobilis</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>Limnäsudden, Dlr</t>
-        </is>
-      </c>
-      <c r="Q18" t="n">
-        <v>516325</v>
-      </c>
-      <c r="R18" t="n">
-        <v>6668756</v>
-      </c>
-      <c r="S18" t="n">
-        <v>5</v>
-      </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>Smedjebacken</t>
-        </is>
-      </c>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>Norrbärke</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>2026-08-09</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>16:58</t>
-        </is>
-      </c>
-      <c r="AA18" t="inlineStr">
-        <is>
-          <t>2026-08-09</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>16:58</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
-        </is>
-      </c>
-      <c r="AD18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT18" t="inlineStr"/>
-      <c r="AW18" t="inlineStr">
-        <is>
-          <t>Alec Bailey</t>
-        </is>
-      </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>Alec Bailey</t>
-        </is>
-      </c>
-      <c r="AY18" t="inlineStr"/>
-      <c r="AZ18" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135775344</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>135775346</v>
-      </c>
-      <c r="B19" t="n">
-        <v>101485</v>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>222498</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Blåsippa</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>Hepatica nobilis</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>Limnäsudden, Dlr</t>
-        </is>
-      </c>
-      <c r="Q19" t="n">
-        <v>516325</v>
-      </c>
-      <c r="R19" t="n">
-        <v>6668729</v>
-      </c>
-      <c r="S19" t="n">
-        <v>5</v>
-      </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="U19" t="inlineStr">
-        <is>
-          <t>Smedjebacken</t>
-        </is>
-      </c>
-      <c r="V19" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>Norrbärke</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>2026-08-09</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>16:59</t>
-        </is>
-      </c>
-      <c r="AA19" t="inlineStr">
-        <is>
-          <t>2026-08-09</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>16:59</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
-        </is>
-      </c>
-      <c r="AD19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT19" t="inlineStr"/>
-      <c r="AW19" t="inlineStr">
-        <is>
-          <t>Alec Bailey</t>
-        </is>
-      </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>Alec Bailey</t>
-        </is>
-      </c>
-      <c r="AY19" t="inlineStr"/>
-      <c r="AZ19" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135775346</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>135775350</v>
-      </c>
-      <c r="B20" t="n">
-        <v>101485</v>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E20" t="n">
-        <v>222498</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Blåsippa</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>Hepatica nobilis</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>Limnäsudden, Dlr</t>
-        </is>
-      </c>
-      <c r="Q20" t="n">
-        <v>516342</v>
-      </c>
-      <c r="R20" t="n">
-        <v>6668692</v>
-      </c>
-      <c r="S20" t="n">
-        <v>5</v>
-      </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="U20" t="inlineStr">
-        <is>
-          <t>Smedjebacken</t>
-        </is>
-      </c>
-      <c r="V20" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>Norrbärke</t>
-        </is>
-      </c>
-      <c r="Y20" t="inlineStr">
-        <is>
-          <t>2026-08-09</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>17:06</t>
-        </is>
-      </c>
-      <c r="AA20" t="inlineStr">
-        <is>
-          <t>2026-08-09</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>17:06</t>
-        </is>
-      </c>
-      <c r="AD20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT20" t="inlineStr"/>
-      <c r="AW20" t="inlineStr">
-        <is>
-          <t>Alec Bailey</t>
-        </is>
-      </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>Alec Bailey</t>
-        </is>
-      </c>
-      <c r="AY20" t="inlineStr"/>
-      <c r="AZ20" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135775350</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>135775354</v>
-      </c>
-      <c r="B21" t="n">
-        <v>101485</v>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E21" t="n">
-        <v>222498</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Blåsippa</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>Hepatica nobilis</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>Limnäsudden, Dlr</t>
-        </is>
-      </c>
-      <c r="Q21" t="n">
-        <v>516349</v>
-      </c>
-      <c r="R21" t="n">
-        <v>6668748</v>
-      </c>
-      <c r="S21" t="n">
-        <v>8</v>
-      </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="U21" t="inlineStr">
-        <is>
-          <t>Smedjebacken</t>
-        </is>
-      </c>
-      <c r="V21" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>Norrbärke</t>
-        </is>
-      </c>
-      <c r="Y21" t="inlineStr">
-        <is>
-          <t>2026-08-09</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>17:21</t>
-        </is>
-      </c>
-      <c r="AA21" t="inlineStr">
-        <is>
-          <t>2026-08-09</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>17:21</t>
-        </is>
-      </c>
-      <c r="AD21" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE21" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG21" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT21" t="inlineStr"/>
-      <c r="AW21" t="inlineStr">
-        <is>
-          <t>Alec Bailey</t>
-        </is>
-      </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>Alec Bailey</t>
-        </is>
-      </c>
-      <c r="AY21" t="inlineStr"/>
-      <c r="AZ21" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135775354</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>135775355</v>
-      </c>
-      <c r="B22" t="n">
-        <v>99082</v>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E22" t="n">
-        <v>223049</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Ormbär</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>Paris quadrifolia</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>Limnäsudden, Dlr</t>
-        </is>
-      </c>
-      <c r="Q22" t="n">
-        <v>516339</v>
-      </c>
-      <c r="R22" t="n">
-        <v>6668746</v>
-      </c>
-      <c r="S22" t="n">
-        <v>12</v>
-      </c>
-      <c r="T22" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="U22" t="inlineStr">
-        <is>
-          <t>Smedjebacken</t>
-        </is>
-      </c>
-      <c r="V22" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>Norrbärke</t>
-        </is>
-      </c>
-      <c r="Y22" t="inlineStr">
-        <is>
-          <t>2026-08-09</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>17:24</t>
-        </is>
-      </c>
-      <c r="AA22" t="inlineStr">
-        <is>
-          <t>2026-08-09</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>17:24</t>
-        </is>
-      </c>
-      <c r="AD22" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE22" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG22" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT22" t="inlineStr"/>
-      <c r="AW22" t="inlineStr">
-        <is>
-          <t>Alec Bailey</t>
-        </is>
-      </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>Alec Bailey</t>
-        </is>
-      </c>
-      <c r="AY22" t="inlineStr"/>
-      <c r="AZ22" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135775355</t>
         </is>
       </c>
     </row>
@@ -3175,15 +2152,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 54940-2025 artfynd.xlsx
+++ b/artfynd/A 54940-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ13"/>
+  <dimension ref="A1:AZ22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -811,10 +811,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>96603593</v>
+        <v>135775340</v>
       </c>
       <c r="B3" t="n">
-        <v>91680</v>
+        <v>96488</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -822,37 +822,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3215</v>
+        <v>2812</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Limnäsudden - Skarvikberget, Dlr</t>
+          <t>Limnäsudden, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>516225</v>
+        <v>516356</v>
       </c>
       <c r="R3" t="n">
-        <v>6668675</v>
+        <v>6668771</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -879,12 +876,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2021-10-11</t>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2021-10-11</t>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -893,44 +900,33 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>kalkmarksskog</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96603593</t>
+          <t>https://artportalen.se/Sighting/135775340</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>96603589</v>
+        <v>96603593</v>
       </c>
       <c r="B4" t="n">
-        <v>92869</v>
+        <v>91680</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -938,21 +934,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4769</v>
+        <v>3215</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -1037,13 +1033,13 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96603589</t>
+          <t>https://artportalen.se/Sighting/96603593</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129974173</v>
+        <v>96603589</v>
       </c>
       <c r="B5" t="n">
         <v>92869</v>
@@ -1077,14 +1073,14 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Skarviksberget, Dlr</t>
+          <t>Limnäsudden - Skarvikberget, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>516220</v>
+        <v>516225</v>
       </c>
       <c r="R5" t="n">
-        <v>6668664</v>
+        <v>6668675</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1111,12 +1107,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2021-10-11</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2021-10-11</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1131,27 +1127,12 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>Lågörtgranskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Inslag av gamla tallar. Kalkmarksskog. Avverkningsplanerat.</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+          <t>kalkmarksskog</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1168,16 +1149,16 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129974173</t>
+          <t>https://artportalen.se/Sighting/96603589</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129974143</v>
+        <v>129974173</v>
       </c>
       <c r="B6" t="n">
-        <v>91282</v>
+        <v>92869</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1185,21 +1166,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5685</v>
+        <v>4769</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1212,10 +1193,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>516272</v>
+        <v>516220</v>
       </c>
       <c r="R6" t="n">
-        <v>6668613</v>
+        <v>6668664</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1272,17 +1253,17 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>tallåga bland gamla granlågor # Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1299,52 +1280,43 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129974143</t>
+          <t>https://artportalen.se/Sighting/129974173</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129974179</v>
+        <v>129974143</v>
       </c>
       <c r="B7" t="n">
-        <v>99118</v>
+        <v>91282</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>5685</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Fr.) Jülich</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1352,10 +1324,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>516259</v>
+        <v>516272</v>
       </c>
       <c r="R7" t="n">
-        <v>6668701</v>
+        <v>6668613</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1410,6 +1382,21 @@
           <t>Inslag av gamla tallar. Kalkmarksskog. Avverkningsplanerat.</t>
         </is>
       </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>tallåga bland gamla granlågor # Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
@@ -1424,63 +1411,51 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129974179</t>
+          <t>https://artportalen.se/Sighting/129974143</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129974211</v>
+        <v>135775349</v>
       </c>
       <c r="B8" t="n">
-        <v>99118</v>
+        <v>4776</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>100299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Skarviksberget, Dlr</t>
+          <t>Limnäsudden, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>516279</v>
+        <v>516333</v>
       </c>
       <c r="R8" t="n">
-        <v>6668684</v>
+        <v>6668702</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1507,12 +1482,27 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>17:05</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Stående död gran, lågörtgranskog</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1521,83 +1511,80 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>Lågörtgranskog</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>Inslag av gamla tallar. Kalkmarksskog. Avverkningsplanerat.</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129974211</t>
+          <t>https://artportalen.se/Sighting/135775349</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>96603576</v>
+        <v>129974179</v>
       </c>
       <c r="B9" t="n">
-        <v>101326</v>
+        <v>99118</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Limnäsudden - Skarvikberget, Dlr</t>
+          <t>Skarviksberget, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>516225</v>
+        <v>516259</v>
       </c>
       <c r="R9" t="n">
-        <v>6668675</v>
+        <v>6668701</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1624,12 +1611,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2021-10-11</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2021-10-11</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1644,12 +1631,12 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Lågörtgranskog</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>kalkmarksskog</t>
+          <t>Inslag av gamla tallar. Kalkmarksskog. Avverkningsplanerat.</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1666,42 +1653,50 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96603576</t>
+          <t>https://artportalen.se/Sighting/129974179</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129974105</v>
+        <v>129974211</v>
       </c>
       <c r="B10" t="n">
-        <v>101325</v>
+        <v>99118</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
@@ -1711,13 +1706,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>516331</v>
+        <v>516279</v>
       </c>
       <c r="R10" t="n">
-        <v>6668692</v>
+        <v>6668684</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1766,7 +1761,7 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>inslag av gamla tallar</t>
+          <t>Inslag av gamla tallar. Kalkmarksskog. Avverkningsplanerat.</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1783,16 +1778,16 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129974105</t>
+          <t>https://artportalen.se/Sighting/129974211</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129974151</v>
+        <v>96603576</v>
       </c>
       <c r="B11" t="n">
-        <v>101325</v>
+        <v>101326</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1824,14 +1819,14 @@
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Skarviksberget, Dlr</t>
+          <t>Limnäsudden - Skarvikberget, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>516214</v>
+        <v>516225</v>
       </c>
       <c r="R11" t="n">
-        <v>6668657</v>
+        <v>6668675</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1858,12 +1853,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2021-10-11</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2021-10-11</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1878,12 +1873,12 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>Lågörtgranskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Inslag av gamla tallar. Kalkmarksskog. Avverkningsplanerat.</t>
+          <t>kalkmarksskog</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1900,13 +1895,13 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129974151</t>
+          <t>https://artportalen.se/Sighting/96603576</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129974181</v>
+        <v>129974105</v>
       </c>
       <c r="B12" t="n">
         <v>101325</v>
@@ -1945,13 +1940,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>516284</v>
+        <v>516331</v>
       </c>
       <c r="R12" t="n">
-        <v>6668713</v>
+        <v>6668692</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2000,7 +1995,7 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Inslag av gamla tallar. Kalkmarksskog. Avverkningsplanerat.</t>
+          <t>inslag av gamla tallar</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2017,13 +2012,13 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129974181</t>
+          <t>https://artportalen.se/Sighting/129974105</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129974196</v>
+        <v>129974151</v>
       </c>
       <c r="B13" t="n">
         <v>101325</v>
@@ -2062,10 +2057,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>516330</v>
+        <v>516214</v>
       </c>
       <c r="R13" t="n">
-        <v>6668614</v>
+        <v>6668657</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2134,7 +2129,1035 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/129974151</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>129974181</v>
+      </c>
+      <c r="B14" t="n">
+        <v>101325</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Skarviksberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>516284</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6668713</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Norrbärke</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>Inslag av gamla tallar. Kalkmarksskog. Avverkningsplanerat.</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129974181</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>129974196</v>
+      </c>
+      <c r="B15" t="n">
+        <v>101325</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Skarviksberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>516330</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6668614</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Norrbärke</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>Inslag av gamla tallar. Kalkmarksskog. Avverkningsplanerat.</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/129974196</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>135775337</v>
+      </c>
+      <c r="B16" t="n">
+        <v>101485</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Limnäsudden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>516387</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6668808</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Norrbärke</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>16:50</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>16:50</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135775337</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>135775341</v>
+      </c>
+      <c r="B17" t="n">
+        <v>101485</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Limnäsudden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>516353</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6668765</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Norrbärke</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>16:54</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>16:54</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135775341</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>135775344</v>
+      </c>
+      <c r="B18" t="n">
+        <v>101485</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Limnäsudden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>516325</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6668756</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Norrbärke</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>16:58</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>16:58</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135775344</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>135775346</v>
+      </c>
+      <c r="B19" t="n">
+        <v>101485</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Limnäsudden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>516325</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6668729</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Norrbärke</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>16:59</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>16:59</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135775346</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>135775350</v>
+      </c>
+      <c r="B20" t="n">
+        <v>101485</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Limnäsudden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>516342</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6668692</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Norrbärke</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>17:06</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>17:06</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135775350</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>135775354</v>
+      </c>
+      <c r="B21" t="n">
+        <v>101485</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Limnäsudden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>516349</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6668748</v>
+      </c>
+      <c r="S21" t="n">
+        <v>8</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Norrbärke</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135775354</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>135775355</v>
+      </c>
+      <c r="B22" t="n">
+        <v>99082</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>223049</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Ormbär</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Paris quadrifolia</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Limnäsudden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>516339</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6668746</v>
+      </c>
+      <c r="S22" t="n">
+        <v>12</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Norrbärke</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>17:24</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>17:24</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135775355</t>
         </is>
       </c>
     </row>
@@ -2152,6 +3175,15 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 54940-2025 artfynd.xlsx
+++ b/artfynd/A 54940-2025 artfynd.xlsx
@@ -814,7 +814,7 @@
         <v>135775340</v>
       </c>
       <c r="B3" t="n">
-        <v>96488</v>
+        <v>96505</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1420,7 +1420,7 @@
         <v>135775349</v>
       </c>
       <c r="B8" t="n">
-        <v>4776</v>
+        <v>4777</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2372,7 +2372,7 @@
         <v>135775337</v>
       </c>
       <c r="B16" t="n">
-        <v>101485</v>
+        <v>101502</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2484,7 +2484,7 @@
         <v>135775341</v>
       </c>
       <c r="B17" t="n">
-        <v>101485</v>
+        <v>101502</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2596,7 +2596,7 @@
         <v>135775344</v>
       </c>
       <c r="B18" t="n">
-        <v>101485</v>
+        <v>101502</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2713,7 +2713,7 @@
         <v>135775346</v>
       </c>
       <c r="B19" t="n">
-        <v>101485</v>
+        <v>101502</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2830,7 +2830,7 @@
         <v>135775350</v>
       </c>
       <c r="B20" t="n">
-        <v>101485</v>
+        <v>101502</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2942,7 +2942,7 @@
         <v>135775354</v>
       </c>
       <c r="B21" t="n">
-        <v>101485</v>
+        <v>101502</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3054,7 +3054,7 @@
         <v>135775355</v>
       </c>
       <c r="B22" t="n">
-        <v>99082</v>
+        <v>99099</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 54940-2025 artfynd.xlsx
+++ b/artfynd/A 54940-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ22"/>
+  <dimension ref="A1:AZ13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -811,10 +811,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>135775340</v>
+        <v>96603593</v>
       </c>
       <c r="B3" t="n">
-        <v>96505</v>
+        <v>91680</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -822,34 +822,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2812</v>
+        <v>3215</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kransmossa</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hylocomiadelphus triquetrus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Ochyra &amp; Stebel</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Limnäsudden, Dlr</t>
+          <t>Limnäsudden - Skarvikberget, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>516356</v>
+        <v>516225</v>
       </c>
       <c r="R3" t="n">
-        <v>6668771</v>
+        <v>6668675</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -876,22 +879,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>16:54</t>
+          <t>2021-10-11</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>16:54</t>
+          <t>2021-10-11</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -900,33 +893,44 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>kalkmarksskog</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135775340</t>
+          <t>https://artportalen.se/Sighting/96603593</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>96603593</v>
+        <v>96603589</v>
       </c>
       <c r="B4" t="n">
-        <v>91680</v>
+        <v>92869</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -934,21 +938,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3215</v>
+        <v>4769</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -1033,13 +1037,13 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96603593</t>
+          <t>https://artportalen.se/Sighting/96603589</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>96603589</v>
+        <v>129974173</v>
       </c>
       <c r="B5" t="n">
         <v>92869</v>
@@ -1073,14 +1077,14 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Limnäsudden - Skarvikberget, Dlr</t>
+          <t>Skarviksberget, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>516225</v>
+        <v>516220</v>
       </c>
       <c r="R5" t="n">
-        <v>6668675</v>
+        <v>6668664</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1107,12 +1111,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2021-10-11</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2021-10-11</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1127,12 +1131,27 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Lågörtgranskog</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>kalkmarksskog</t>
+          <t>Inslag av gamla tallar. Kalkmarksskog. Avverkningsplanerat.</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1149,16 +1168,16 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96603589</t>
+          <t>https://artportalen.se/Sighting/129974173</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129974173</v>
+        <v>129974143</v>
       </c>
       <c r="B6" t="n">
-        <v>92869</v>
+        <v>91282</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1166,21 +1185,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4769</v>
+        <v>5685</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1193,10 +1212,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>516220</v>
+        <v>516272</v>
       </c>
       <c r="R6" t="n">
-        <v>6668664</v>
+        <v>6668613</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1253,17 +1272,17 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>tallåga bland gamla granlågor # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1280,43 +1299,52 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129974173</t>
+          <t>https://artportalen.se/Sighting/129974143</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129974143</v>
+        <v>129974179</v>
       </c>
       <c r="B7" t="n">
-        <v>91282</v>
+        <v>99118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5685</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1324,10 +1352,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>516272</v>
+        <v>516259</v>
       </c>
       <c r="R7" t="n">
-        <v>6668613</v>
+        <v>6668701</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1382,21 +1410,6 @@
           <t>Inslag av gamla tallar. Kalkmarksskog. Avverkningsplanerat.</t>
         </is>
       </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>tallåga bland gamla granlågor # Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
@@ -1411,51 +1424,63 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129974143</t>
+          <t>https://artportalen.se/Sighting/129974179</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>135775349</v>
+        <v>129974211</v>
       </c>
       <c r="B8" t="n">
-        <v>4777</v>
+        <v>99118</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100299</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Limnäsudden, Dlr</t>
+          <t>Skarviksberget, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>516333</v>
+        <v>516279</v>
       </c>
       <c r="R8" t="n">
-        <v>6668702</v>
+        <v>6668684</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1482,27 +1507,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>17:05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>17:05</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Stående död gran, lågörtgranskog</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1511,80 +1521,83 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Inslag av gamla tallar. Kalkmarksskog. Avverkningsplanerat.</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135775349</t>
+          <t>https://artportalen.se/Sighting/129974211</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129974179</v>
+        <v>96603576</v>
       </c>
       <c r="B9" t="n">
-        <v>99118</v>
+        <v>101326</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Skarviksberget, Dlr</t>
+          <t>Limnäsudden - Skarvikberget, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>516259</v>
+        <v>516225</v>
       </c>
       <c r="R9" t="n">
-        <v>6668701</v>
+        <v>6668675</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1611,12 +1624,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2021-10-11</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2021-10-11</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1631,12 +1644,12 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>Lågörtgranskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Inslag av gamla tallar. Kalkmarksskog. Avverkningsplanerat.</t>
+          <t>kalkmarksskog</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1653,50 +1666,42 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129974179</t>
+          <t>https://artportalen.se/Sighting/96603576</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129974211</v>
+        <v>129974105</v>
       </c>
       <c r="B10" t="n">
-        <v>99118</v>
+        <v>101325</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
@@ -1706,13 +1711,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>516279</v>
+        <v>516331</v>
       </c>
       <c r="R10" t="n">
-        <v>6668684</v>
+        <v>6668692</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1761,7 +1766,7 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Inslag av gamla tallar. Kalkmarksskog. Avverkningsplanerat.</t>
+          <t>inslag av gamla tallar</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1778,16 +1783,16 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129974211</t>
+          <t>https://artportalen.se/Sighting/129974105</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>96603576</v>
+        <v>129974151</v>
       </c>
       <c r="B11" t="n">
-        <v>101326</v>
+        <v>101325</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1819,14 +1824,14 @@
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Limnäsudden - Skarvikberget, Dlr</t>
+          <t>Skarviksberget, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>516225</v>
+        <v>516214</v>
       </c>
       <c r="R11" t="n">
-        <v>6668675</v>
+        <v>6668657</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1853,12 +1858,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2021-10-11</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2021-10-11</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1873,12 +1878,12 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Lågörtgranskog</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>kalkmarksskog</t>
+          <t>Inslag av gamla tallar. Kalkmarksskog. Avverkningsplanerat.</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1895,13 +1900,13 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96603576</t>
+          <t>https://artportalen.se/Sighting/129974151</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129974105</v>
+        <v>129974181</v>
       </c>
       <c r="B12" t="n">
         <v>101325</v>
@@ -1940,13 +1945,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>516331</v>
+        <v>516284</v>
       </c>
       <c r="R12" t="n">
-        <v>6668692</v>
+        <v>6668713</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1995,7 +2000,7 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>inslag av gamla tallar</t>
+          <t>Inslag av gamla tallar. Kalkmarksskog. Avverkningsplanerat.</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2012,13 +2017,13 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129974105</t>
+          <t>https://artportalen.se/Sighting/129974181</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129974151</v>
+        <v>129974196</v>
       </c>
       <c r="B13" t="n">
         <v>101325</v>
@@ -2057,10 +2062,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>516214</v>
+        <v>516330</v>
       </c>
       <c r="R13" t="n">
-        <v>6668657</v>
+        <v>6668614</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2129,1035 +2134,7 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129974151</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>129974181</v>
-      </c>
-      <c r="B14" t="n">
-        <v>101325</v>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>222498</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Blåsippa</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>Hepatica nobilis</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>Skarviksberget, Dlr</t>
-        </is>
-      </c>
-      <c r="Q14" t="n">
-        <v>516284</v>
-      </c>
-      <c r="R14" t="n">
-        <v>6668713</v>
-      </c>
-      <c r="S14" t="n">
-        <v>5</v>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>Smedjebacken</t>
-        </is>
-      </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>Norrbärke</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>2025-12-04</t>
-        </is>
-      </c>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t>2025-12-04</t>
-        </is>
-      </c>
-      <c r="AD14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF14" t="inlineStr"/>
-      <c r="AG14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>Lågörtgranskog</t>
-        </is>
-      </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>Inslag av gamla tallar. Kalkmarksskog. Avverkningsplanerat.</t>
-        </is>
-      </c>
-      <c r="AT14" t="inlineStr"/>
-      <c r="AW14" t="inlineStr">
-        <is>
-          <t>Janolof Hermansson</t>
-        </is>
-      </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>Janolof Hermansson</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr"/>
-      <c r="AZ14" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/129974181</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>129974196</v>
-      </c>
-      <c r="B15" t="n">
-        <v>101325</v>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>222498</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Blåsippa</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Hepatica nobilis</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>Skarviksberget, Dlr</t>
-        </is>
-      </c>
-      <c r="Q15" t="n">
-        <v>516330</v>
-      </c>
-      <c r="R15" t="n">
-        <v>6668614</v>
-      </c>
-      <c r="S15" t="n">
-        <v>5</v>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>Smedjebacken</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>Norrbärke</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>2025-12-04</t>
-        </is>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>2025-12-04</t>
-        </is>
-      </c>
-      <c r="AD15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF15" t="inlineStr"/>
-      <c r="AG15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>Lågörtgranskog</t>
-        </is>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>Inslag av gamla tallar. Kalkmarksskog. Avverkningsplanerat.</t>
-        </is>
-      </c>
-      <c r="AT15" t="inlineStr"/>
-      <c r="AW15" t="inlineStr">
-        <is>
-          <t>Janolof Hermansson</t>
-        </is>
-      </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>Janolof Hermansson</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr"/>
-      <c r="AZ15" t="inlineStr">
-        <is>
           <t>https://artportalen.se/Sighting/129974196</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>135775337</v>
-      </c>
-      <c r="B16" t="n">
-        <v>101502</v>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>222498</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Blåsippa</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>Hepatica nobilis</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>Limnäsudden, Dlr</t>
-        </is>
-      </c>
-      <c r="Q16" t="n">
-        <v>516387</v>
-      </c>
-      <c r="R16" t="n">
-        <v>6668808</v>
-      </c>
-      <c r="S16" t="n">
-        <v>5</v>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>Smedjebacken</t>
-        </is>
-      </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>Norrbärke</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>2026-08-09</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>16:50</t>
-        </is>
-      </c>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>2026-08-09</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>16:50</t>
-        </is>
-      </c>
-      <c r="AD16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT16" t="inlineStr"/>
-      <c r="AW16" t="inlineStr">
-        <is>
-          <t>Alec Bailey</t>
-        </is>
-      </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>Alec Bailey</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr"/>
-      <c r="AZ16" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135775337</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>135775341</v>
-      </c>
-      <c r="B17" t="n">
-        <v>101502</v>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>222498</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Blåsippa</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Hepatica nobilis</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>Limnäsudden, Dlr</t>
-        </is>
-      </c>
-      <c r="Q17" t="n">
-        <v>516353</v>
-      </c>
-      <c r="R17" t="n">
-        <v>6668765</v>
-      </c>
-      <c r="S17" t="n">
-        <v>5</v>
-      </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>Smedjebacken</t>
-        </is>
-      </c>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>Norrbärke</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>2026-08-09</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>16:54</t>
-        </is>
-      </c>
-      <c r="AA17" t="inlineStr">
-        <is>
-          <t>2026-08-09</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>16:54</t>
-        </is>
-      </c>
-      <c r="AD17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT17" t="inlineStr"/>
-      <c r="AW17" t="inlineStr">
-        <is>
-          <t>Alec Bailey</t>
-        </is>
-      </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>Alec Bailey</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr"/>
-      <c r="AZ17" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135775341</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>135775344</v>
-      </c>
-      <c r="B18" t="n">
-        <v>101502</v>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>222498</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Blåsippa</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>Hepatica nobilis</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>Limnäsudden, Dlr</t>
-        </is>
-      </c>
-      <c r="Q18" t="n">
-        <v>516325</v>
-      </c>
-      <c r="R18" t="n">
-        <v>6668756</v>
-      </c>
-      <c r="S18" t="n">
-        <v>5</v>
-      </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>Smedjebacken</t>
-        </is>
-      </c>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>Norrbärke</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>2026-08-09</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>16:58</t>
-        </is>
-      </c>
-      <c r="AA18" t="inlineStr">
-        <is>
-          <t>2026-08-09</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>16:58</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
-        </is>
-      </c>
-      <c r="AD18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT18" t="inlineStr"/>
-      <c r="AW18" t="inlineStr">
-        <is>
-          <t>Alec Bailey</t>
-        </is>
-      </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>Alec Bailey</t>
-        </is>
-      </c>
-      <c r="AY18" t="inlineStr"/>
-      <c r="AZ18" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135775344</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>135775346</v>
-      </c>
-      <c r="B19" t="n">
-        <v>101502</v>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>222498</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Blåsippa</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>Hepatica nobilis</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>Limnäsudden, Dlr</t>
-        </is>
-      </c>
-      <c r="Q19" t="n">
-        <v>516325</v>
-      </c>
-      <c r="R19" t="n">
-        <v>6668729</v>
-      </c>
-      <c r="S19" t="n">
-        <v>5</v>
-      </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="U19" t="inlineStr">
-        <is>
-          <t>Smedjebacken</t>
-        </is>
-      </c>
-      <c r="V19" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>Norrbärke</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>2026-08-09</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>16:59</t>
-        </is>
-      </c>
-      <c r="AA19" t="inlineStr">
-        <is>
-          <t>2026-08-09</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>16:59</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
-        </is>
-      </c>
-      <c r="AD19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT19" t="inlineStr"/>
-      <c r="AW19" t="inlineStr">
-        <is>
-          <t>Alec Bailey</t>
-        </is>
-      </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>Alec Bailey</t>
-        </is>
-      </c>
-      <c r="AY19" t="inlineStr"/>
-      <c r="AZ19" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135775346</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>135775350</v>
-      </c>
-      <c r="B20" t="n">
-        <v>101502</v>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E20" t="n">
-        <v>222498</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Blåsippa</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>Hepatica nobilis</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>Limnäsudden, Dlr</t>
-        </is>
-      </c>
-      <c r="Q20" t="n">
-        <v>516342</v>
-      </c>
-      <c r="R20" t="n">
-        <v>6668692</v>
-      </c>
-      <c r="S20" t="n">
-        <v>5</v>
-      </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="U20" t="inlineStr">
-        <is>
-          <t>Smedjebacken</t>
-        </is>
-      </c>
-      <c r="V20" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>Norrbärke</t>
-        </is>
-      </c>
-      <c r="Y20" t="inlineStr">
-        <is>
-          <t>2026-08-09</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>17:06</t>
-        </is>
-      </c>
-      <c r="AA20" t="inlineStr">
-        <is>
-          <t>2026-08-09</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>17:06</t>
-        </is>
-      </c>
-      <c r="AD20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT20" t="inlineStr"/>
-      <c r="AW20" t="inlineStr">
-        <is>
-          <t>Alec Bailey</t>
-        </is>
-      </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>Alec Bailey</t>
-        </is>
-      </c>
-      <c r="AY20" t="inlineStr"/>
-      <c r="AZ20" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135775350</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>135775354</v>
-      </c>
-      <c r="B21" t="n">
-        <v>101502</v>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E21" t="n">
-        <v>222498</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Blåsippa</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>Hepatica nobilis</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>Limnäsudden, Dlr</t>
-        </is>
-      </c>
-      <c r="Q21" t="n">
-        <v>516349</v>
-      </c>
-      <c r="R21" t="n">
-        <v>6668748</v>
-      </c>
-      <c r="S21" t="n">
-        <v>8</v>
-      </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="U21" t="inlineStr">
-        <is>
-          <t>Smedjebacken</t>
-        </is>
-      </c>
-      <c r="V21" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>Norrbärke</t>
-        </is>
-      </c>
-      <c r="Y21" t="inlineStr">
-        <is>
-          <t>2026-08-09</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>17:21</t>
-        </is>
-      </c>
-      <c r="AA21" t="inlineStr">
-        <is>
-          <t>2026-08-09</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>17:21</t>
-        </is>
-      </c>
-      <c r="AD21" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE21" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG21" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT21" t="inlineStr"/>
-      <c r="AW21" t="inlineStr">
-        <is>
-          <t>Alec Bailey</t>
-        </is>
-      </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>Alec Bailey</t>
-        </is>
-      </c>
-      <c r="AY21" t="inlineStr"/>
-      <c r="AZ21" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135775354</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>135775355</v>
-      </c>
-      <c r="B22" t="n">
-        <v>99099</v>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E22" t="n">
-        <v>223049</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Ormbär</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>Paris quadrifolia</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>Limnäsudden, Dlr</t>
-        </is>
-      </c>
-      <c r="Q22" t="n">
-        <v>516339</v>
-      </c>
-      <c r="R22" t="n">
-        <v>6668746</v>
-      </c>
-      <c r="S22" t="n">
-        <v>12</v>
-      </c>
-      <c r="T22" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="U22" t="inlineStr">
-        <is>
-          <t>Smedjebacken</t>
-        </is>
-      </c>
-      <c r="V22" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>Norrbärke</t>
-        </is>
-      </c>
-      <c r="Y22" t="inlineStr">
-        <is>
-          <t>2026-08-09</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>17:24</t>
-        </is>
-      </c>
-      <c r="AA22" t="inlineStr">
-        <is>
-          <t>2026-08-09</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>17:24</t>
-        </is>
-      </c>
-      <c r="AD22" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE22" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG22" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT22" t="inlineStr"/>
-      <c r="AW22" t="inlineStr">
-        <is>
-          <t>Alec Bailey</t>
-        </is>
-      </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>Alec Bailey</t>
-        </is>
-      </c>
-      <c r="AY22" t="inlineStr"/>
-      <c r="AZ22" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135775355</t>
         </is>
       </c>
     </row>
@@ -3175,15 +2152,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 54940-2025 artfynd.xlsx
+++ b/artfynd/A 54940-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ13"/>
+  <dimension ref="A1:AZ22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -811,10 +811,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>96603593</v>
+        <v>135775340</v>
       </c>
       <c r="B3" t="n">
-        <v>91680</v>
+        <v>96505</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -822,37 +822,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3215</v>
+        <v>2812</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Limnäsudden - Skarvikberget, Dlr</t>
+          <t>Limnäsudden, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>516225</v>
+        <v>516356</v>
       </c>
       <c r="R3" t="n">
-        <v>6668675</v>
+        <v>6668771</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -879,12 +876,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2021-10-11</t>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2021-10-11</t>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -893,44 +900,33 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>kalkmarksskog</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96603593</t>
+          <t>https://artportalen.se/Sighting/135775340</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>96603589</v>
+        <v>96603593</v>
       </c>
       <c r="B4" t="n">
-        <v>92869</v>
+        <v>91680</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -938,21 +934,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4769</v>
+        <v>3215</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -1037,13 +1033,13 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96603589</t>
+          <t>https://artportalen.se/Sighting/96603593</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129974173</v>
+        <v>96603589</v>
       </c>
       <c r="B5" t="n">
         <v>92869</v>
@@ -1077,14 +1073,14 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Skarviksberget, Dlr</t>
+          <t>Limnäsudden - Skarvikberget, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>516220</v>
+        <v>516225</v>
       </c>
       <c r="R5" t="n">
-        <v>6668664</v>
+        <v>6668675</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1111,12 +1107,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2021-10-11</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2021-10-11</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1131,27 +1127,12 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>Lågörtgranskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Inslag av gamla tallar. Kalkmarksskog. Avverkningsplanerat.</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+          <t>kalkmarksskog</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1168,16 +1149,16 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129974173</t>
+          <t>https://artportalen.se/Sighting/96603589</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129974143</v>
+        <v>129974173</v>
       </c>
       <c r="B6" t="n">
-        <v>91282</v>
+        <v>92869</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1185,21 +1166,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5685</v>
+        <v>4769</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1212,10 +1193,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>516272</v>
+        <v>516220</v>
       </c>
       <c r="R6" t="n">
-        <v>6668613</v>
+        <v>6668664</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1272,17 +1253,17 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>tallåga bland gamla granlågor # Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1299,52 +1280,43 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129974143</t>
+          <t>https://artportalen.se/Sighting/129974173</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129974179</v>
+        <v>129974143</v>
       </c>
       <c r="B7" t="n">
-        <v>99118</v>
+        <v>91282</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>5685</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Fr.) Jülich</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1352,10 +1324,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>516259</v>
+        <v>516272</v>
       </c>
       <c r="R7" t="n">
-        <v>6668701</v>
+        <v>6668613</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1410,6 +1382,21 @@
           <t>Inslag av gamla tallar. Kalkmarksskog. Avverkningsplanerat.</t>
         </is>
       </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>tallåga bland gamla granlågor # Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
@@ -1424,63 +1411,51 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129974179</t>
+          <t>https://artportalen.se/Sighting/129974143</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129974211</v>
+        <v>135775349</v>
       </c>
       <c r="B8" t="n">
-        <v>99118</v>
+        <v>4777</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>100299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Skarviksberget, Dlr</t>
+          <t>Limnäsudden, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>516279</v>
+        <v>516333</v>
       </c>
       <c r="R8" t="n">
-        <v>6668684</v>
+        <v>6668702</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1507,12 +1482,27 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>17:05</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Stående död gran, lågörtgranskog</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1521,83 +1511,80 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>Lågörtgranskog</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>Inslag av gamla tallar. Kalkmarksskog. Avverkningsplanerat.</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129974211</t>
+          <t>https://artportalen.se/Sighting/135775349</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>96603576</v>
+        <v>129974179</v>
       </c>
       <c r="B9" t="n">
-        <v>101326</v>
+        <v>99118</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Limnäsudden - Skarvikberget, Dlr</t>
+          <t>Skarviksberget, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>516225</v>
+        <v>516259</v>
       </c>
       <c r="R9" t="n">
-        <v>6668675</v>
+        <v>6668701</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1624,12 +1611,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2021-10-11</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2021-10-11</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1644,12 +1631,12 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Lågörtgranskog</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>kalkmarksskog</t>
+          <t>Inslag av gamla tallar. Kalkmarksskog. Avverkningsplanerat.</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1666,42 +1653,50 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96603576</t>
+          <t>https://artportalen.se/Sighting/129974179</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129974105</v>
+        <v>129974211</v>
       </c>
       <c r="B10" t="n">
-        <v>101325</v>
+        <v>99118</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
@@ -1711,13 +1706,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>516331</v>
+        <v>516279</v>
       </c>
       <c r="R10" t="n">
-        <v>6668692</v>
+        <v>6668684</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1766,7 +1761,7 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>inslag av gamla tallar</t>
+          <t>Inslag av gamla tallar. Kalkmarksskog. Avverkningsplanerat.</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1783,16 +1778,16 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129974105</t>
+          <t>https://artportalen.se/Sighting/129974211</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129974151</v>
+        <v>96603576</v>
       </c>
       <c r="B11" t="n">
-        <v>101325</v>
+        <v>101326</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1824,14 +1819,14 @@
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Skarviksberget, Dlr</t>
+          <t>Limnäsudden - Skarvikberget, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>516214</v>
+        <v>516225</v>
       </c>
       <c r="R11" t="n">
-        <v>6668657</v>
+        <v>6668675</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1858,12 +1853,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2021-10-11</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2021-10-11</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1878,12 +1873,12 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>Lågörtgranskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Inslag av gamla tallar. Kalkmarksskog. Avverkningsplanerat.</t>
+          <t>kalkmarksskog</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1900,13 +1895,13 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129974151</t>
+          <t>https://artportalen.se/Sighting/96603576</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129974181</v>
+        <v>129974105</v>
       </c>
       <c r="B12" t="n">
         <v>101325</v>
@@ -1945,13 +1940,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>516284</v>
+        <v>516331</v>
       </c>
       <c r="R12" t="n">
-        <v>6668713</v>
+        <v>6668692</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2000,7 +1995,7 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Inslag av gamla tallar. Kalkmarksskog. Avverkningsplanerat.</t>
+          <t>inslag av gamla tallar</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2017,13 +2012,13 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129974181</t>
+          <t>https://artportalen.se/Sighting/129974105</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129974196</v>
+        <v>129974151</v>
       </c>
       <c r="B13" t="n">
         <v>101325</v>
@@ -2062,10 +2057,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>516330</v>
+        <v>516214</v>
       </c>
       <c r="R13" t="n">
-        <v>6668614</v>
+        <v>6668657</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2134,7 +2129,1035 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/129974151</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>129974181</v>
+      </c>
+      <c r="B14" t="n">
+        <v>101325</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Skarviksberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>516284</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6668713</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Norrbärke</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>Inslag av gamla tallar. Kalkmarksskog. Avverkningsplanerat.</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129974181</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>129974196</v>
+      </c>
+      <c r="B15" t="n">
+        <v>101325</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Skarviksberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>516330</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6668614</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Norrbärke</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>Inslag av gamla tallar. Kalkmarksskog. Avverkningsplanerat.</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/129974196</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>135775337</v>
+      </c>
+      <c r="B16" t="n">
+        <v>101502</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Limnäsudden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>516387</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6668808</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Norrbärke</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>16:50</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>16:50</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135775337</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>135775341</v>
+      </c>
+      <c r="B17" t="n">
+        <v>101502</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Limnäsudden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>516353</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6668765</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Norrbärke</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>16:54</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>16:54</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135775341</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>135775344</v>
+      </c>
+      <c r="B18" t="n">
+        <v>101502</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Limnäsudden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>516325</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6668756</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Norrbärke</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>16:58</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>16:58</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135775344</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>135775346</v>
+      </c>
+      <c r="B19" t="n">
+        <v>101502</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Limnäsudden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>516325</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6668729</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Norrbärke</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>16:59</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>16:59</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135775346</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>135775350</v>
+      </c>
+      <c r="B20" t="n">
+        <v>101502</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Limnäsudden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>516342</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6668692</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Norrbärke</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>17:06</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>17:06</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135775350</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>135775354</v>
+      </c>
+      <c r="B21" t="n">
+        <v>101502</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Limnäsudden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>516349</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6668748</v>
+      </c>
+      <c r="S21" t="n">
+        <v>8</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Norrbärke</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135775354</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>135775355</v>
+      </c>
+      <c r="B22" t="n">
+        <v>99099</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>223049</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Ormbär</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Paris quadrifolia</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Limnäsudden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>516339</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6668746</v>
+      </c>
+      <c r="S22" t="n">
+        <v>12</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Norrbärke</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>17:24</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>17:24</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135775355</t>
         </is>
       </c>
     </row>
@@ -2152,6 +3175,15 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 54940-2025 artfynd.xlsx
+++ b/artfynd/A 54940-2025 artfynd.xlsx
@@ -814,7 +814,7 @@
         <v>135775340</v>
       </c>
       <c r="B3" t="n">
-        <v>96505</v>
+        <v>96506</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -2372,7 +2372,7 @@
         <v>135775337</v>
       </c>
       <c r="B16" t="n">
-        <v>101502</v>
+        <v>101504</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2484,7 +2484,7 @@
         <v>135775341</v>
       </c>
       <c r="B17" t="n">
-        <v>101502</v>
+        <v>101504</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2596,7 +2596,7 @@
         <v>135775344</v>
       </c>
       <c r="B18" t="n">
-        <v>101502</v>
+        <v>101504</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2713,7 +2713,7 @@
         <v>135775346</v>
       </c>
       <c r="B19" t="n">
-        <v>101502</v>
+        <v>101504</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2830,7 +2830,7 @@
         <v>135775350</v>
       </c>
       <c r="B20" t="n">
-        <v>101502</v>
+        <v>101504</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2942,7 +2942,7 @@
         <v>135775354</v>
       </c>
       <c r="B21" t="n">
-        <v>101502</v>
+        <v>101504</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3054,7 +3054,7 @@
         <v>135775355</v>
       </c>
       <c r="B22" t="n">
-        <v>99099</v>
+        <v>99100</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 54940-2025 artfynd.xlsx
+++ b/artfynd/A 54940-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ22"/>
+  <dimension ref="A1:AZ13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -811,10 +811,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>135775340</v>
+        <v>96603593</v>
       </c>
       <c r="B3" t="n">
-        <v>96506</v>
+        <v>91680</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -822,34 +822,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2812</v>
+        <v>3215</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kransmossa</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hylocomiadelphus triquetrus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Ochyra &amp; Stebel</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Limnäsudden, Dlr</t>
+          <t>Limnäsudden - Skarvikberget, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>516356</v>
+        <v>516225</v>
       </c>
       <c r="R3" t="n">
-        <v>6668771</v>
+        <v>6668675</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -876,22 +879,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>16:54</t>
+          <t>2021-10-11</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>16:54</t>
+          <t>2021-10-11</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -900,33 +893,44 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>kalkmarksskog</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135775340</t>
+          <t>https://artportalen.se/Sighting/96603593</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>96603593</v>
+        <v>96603589</v>
       </c>
       <c r="B4" t="n">
-        <v>91680</v>
+        <v>92869</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -934,21 +938,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3215</v>
+        <v>4769</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -1033,13 +1037,13 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96603593</t>
+          <t>https://artportalen.se/Sighting/96603589</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>96603589</v>
+        <v>129974173</v>
       </c>
       <c r="B5" t="n">
         <v>92869</v>
@@ -1073,14 +1077,14 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Limnäsudden - Skarvikberget, Dlr</t>
+          <t>Skarviksberget, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>516225</v>
+        <v>516220</v>
       </c>
       <c r="R5" t="n">
-        <v>6668675</v>
+        <v>6668664</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1107,12 +1111,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2021-10-11</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2021-10-11</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1127,12 +1131,27 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Lågörtgranskog</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>kalkmarksskog</t>
+          <t>Inslag av gamla tallar. Kalkmarksskog. Avverkningsplanerat.</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1149,16 +1168,16 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96603589</t>
+          <t>https://artportalen.se/Sighting/129974173</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129974173</v>
+        <v>129974143</v>
       </c>
       <c r="B6" t="n">
-        <v>92869</v>
+        <v>91282</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1166,21 +1185,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4769</v>
+        <v>5685</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1193,10 +1212,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>516220</v>
+        <v>516272</v>
       </c>
       <c r="R6" t="n">
-        <v>6668664</v>
+        <v>6668613</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1253,17 +1272,17 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>tallåga bland gamla granlågor # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1280,43 +1299,52 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129974173</t>
+          <t>https://artportalen.se/Sighting/129974143</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129974143</v>
+        <v>129974179</v>
       </c>
       <c r="B7" t="n">
-        <v>91282</v>
+        <v>99118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5685</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1324,10 +1352,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>516272</v>
+        <v>516259</v>
       </c>
       <c r="R7" t="n">
-        <v>6668613</v>
+        <v>6668701</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1382,21 +1410,6 @@
           <t>Inslag av gamla tallar. Kalkmarksskog. Avverkningsplanerat.</t>
         </is>
       </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>tallåga bland gamla granlågor # Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
@@ -1411,51 +1424,63 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129974143</t>
+          <t>https://artportalen.se/Sighting/129974179</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>135775349</v>
+        <v>129974211</v>
       </c>
       <c r="B8" t="n">
-        <v>4777</v>
+        <v>99118</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100299</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Limnäsudden, Dlr</t>
+          <t>Skarviksberget, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>516333</v>
+        <v>516279</v>
       </c>
       <c r="R8" t="n">
-        <v>6668702</v>
+        <v>6668684</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1482,27 +1507,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>17:05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>17:05</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Stående död gran, lågörtgranskog</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1511,80 +1521,83 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Inslag av gamla tallar. Kalkmarksskog. Avverkningsplanerat.</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135775349</t>
+          <t>https://artportalen.se/Sighting/129974211</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129974179</v>
+        <v>96603576</v>
       </c>
       <c r="B9" t="n">
-        <v>99118</v>
+        <v>101326</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Skarviksberget, Dlr</t>
+          <t>Limnäsudden - Skarvikberget, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>516259</v>
+        <v>516225</v>
       </c>
       <c r="R9" t="n">
-        <v>6668701</v>
+        <v>6668675</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1611,12 +1624,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2021-10-11</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2021-10-11</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1631,12 +1644,12 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>Lågörtgranskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Inslag av gamla tallar. Kalkmarksskog. Avverkningsplanerat.</t>
+          <t>kalkmarksskog</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1653,50 +1666,42 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129974179</t>
+          <t>https://artportalen.se/Sighting/96603576</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129974211</v>
+        <v>129974105</v>
       </c>
       <c r="B10" t="n">
-        <v>99118</v>
+        <v>101325</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
@@ -1706,13 +1711,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>516279</v>
+        <v>516331</v>
       </c>
       <c r="R10" t="n">
-        <v>6668684</v>
+        <v>6668692</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1761,7 +1766,7 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Inslag av gamla tallar. Kalkmarksskog. Avverkningsplanerat.</t>
+          <t>inslag av gamla tallar</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1778,16 +1783,16 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129974211</t>
+          <t>https://artportalen.se/Sighting/129974105</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>96603576</v>
+        <v>129974151</v>
       </c>
       <c r="B11" t="n">
-        <v>101326</v>
+        <v>101325</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1819,14 +1824,14 @@
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Limnäsudden - Skarvikberget, Dlr</t>
+          <t>Skarviksberget, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>516225</v>
+        <v>516214</v>
       </c>
       <c r="R11" t="n">
-        <v>6668675</v>
+        <v>6668657</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1853,12 +1858,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2021-10-11</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2021-10-11</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1873,12 +1878,12 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Lågörtgranskog</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>kalkmarksskog</t>
+          <t>Inslag av gamla tallar. Kalkmarksskog. Avverkningsplanerat.</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1895,13 +1900,13 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96603576</t>
+          <t>https://artportalen.se/Sighting/129974151</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129974105</v>
+        <v>129974181</v>
       </c>
       <c r="B12" t="n">
         <v>101325</v>
@@ -1940,13 +1945,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>516331</v>
+        <v>516284</v>
       </c>
       <c r="R12" t="n">
-        <v>6668692</v>
+        <v>6668713</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1995,7 +2000,7 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>inslag av gamla tallar</t>
+          <t>Inslag av gamla tallar. Kalkmarksskog. Avverkningsplanerat.</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2012,13 +2017,13 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129974105</t>
+          <t>https://artportalen.se/Sighting/129974181</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129974151</v>
+        <v>129974196</v>
       </c>
       <c r="B13" t="n">
         <v>101325</v>
@@ -2057,10 +2062,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>516214</v>
+        <v>516330</v>
       </c>
       <c r="R13" t="n">
-        <v>6668657</v>
+        <v>6668614</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2129,1035 +2134,7 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129974151</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>129974181</v>
-      </c>
-      <c r="B14" t="n">
-        <v>101325</v>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>222498</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Blåsippa</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>Hepatica nobilis</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>Skarviksberget, Dlr</t>
-        </is>
-      </c>
-      <c r="Q14" t="n">
-        <v>516284</v>
-      </c>
-      <c r="R14" t="n">
-        <v>6668713</v>
-      </c>
-      <c r="S14" t="n">
-        <v>5</v>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>Smedjebacken</t>
-        </is>
-      </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>Norrbärke</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>2025-12-04</t>
-        </is>
-      </c>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t>2025-12-04</t>
-        </is>
-      </c>
-      <c r="AD14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF14" t="inlineStr"/>
-      <c r="AG14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>Lågörtgranskog</t>
-        </is>
-      </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>Inslag av gamla tallar. Kalkmarksskog. Avverkningsplanerat.</t>
-        </is>
-      </c>
-      <c r="AT14" t="inlineStr"/>
-      <c r="AW14" t="inlineStr">
-        <is>
-          <t>Janolof Hermansson</t>
-        </is>
-      </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>Janolof Hermansson</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr"/>
-      <c r="AZ14" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/129974181</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>129974196</v>
-      </c>
-      <c r="B15" t="n">
-        <v>101325</v>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>222498</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Blåsippa</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Hepatica nobilis</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>Skarviksberget, Dlr</t>
-        </is>
-      </c>
-      <c r="Q15" t="n">
-        <v>516330</v>
-      </c>
-      <c r="R15" t="n">
-        <v>6668614</v>
-      </c>
-      <c r="S15" t="n">
-        <v>5</v>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>Smedjebacken</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>Norrbärke</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>2025-12-04</t>
-        </is>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>2025-12-04</t>
-        </is>
-      </c>
-      <c r="AD15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF15" t="inlineStr"/>
-      <c r="AG15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>Lågörtgranskog</t>
-        </is>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>Inslag av gamla tallar. Kalkmarksskog. Avverkningsplanerat.</t>
-        </is>
-      </c>
-      <c r="AT15" t="inlineStr"/>
-      <c r="AW15" t="inlineStr">
-        <is>
-          <t>Janolof Hermansson</t>
-        </is>
-      </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>Janolof Hermansson</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr"/>
-      <c r="AZ15" t="inlineStr">
-        <is>
           <t>https://artportalen.se/Sighting/129974196</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>135775337</v>
-      </c>
-      <c r="B16" t="n">
-        <v>101504</v>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>222498</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Blåsippa</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>Hepatica nobilis</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>Limnäsudden, Dlr</t>
-        </is>
-      </c>
-      <c r="Q16" t="n">
-        <v>516387</v>
-      </c>
-      <c r="R16" t="n">
-        <v>6668808</v>
-      </c>
-      <c r="S16" t="n">
-        <v>5</v>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>Smedjebacken</t>
-        </is>
-      </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>Norrbärke</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>2026-08-09</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>16:50</t>
-        </is>
-      </c>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>2026-08-09</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>16:50</t>
-        </is>
-      </c>
-      <c r="AD16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT16" t="inlineStr"/>
-      <c r="AW16" t="inlineStr">
-        <is>
-          <t>Alec Bailey</t>
-        </is>
-      </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>Alec Bailey</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr"/>
-      <c r="AZ16" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135775337</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>135775341</v>
-      </c>
-      <c r="B17" t="n">
-        <v>101504</v>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>222498</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Blåsippa</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Hepatica nobilis</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>Limnäsudden, Dlr</t>
-        </is>
-      </c>
-      <c r="Q17" t="n">
-        <v>516353</v>
-      </c>
-      <c r="R17" t="n">
-        <v>6668765</v>
-      </c>
-      <c r="S17" t="n">
-        <v>5</v>
-      </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>Smedjebacken</t>
-        </is>
-      </c>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>Norrbärke</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>2026-08-09</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>16:54</t>
-        </is>
-      </c>
-      <c r="AA17" t="inlineStr">
-        <is>
-          <t>2026-08-09</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>16:54</t>
-        </is>
-      </c>
-      <c r="AD17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT17" t="inlineStr"/>
-      <c r="AW17" t="inlineStr">
-        <is>
-          <t>Alec Bailey</t>
-        </is>
-      </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>Alec Bailey</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr"/>
-      <c r="AZ17" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135775341</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>135775344</v>
-      </c>
-      <c r="B18" t="n">
-        <v>101504</v>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>222498</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Blåsippa</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>Hepatica nobilis</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>Limnäsudden, Dlr</t>
-        </is>
-      </c>
-      <c r="Q18" t="n">
-        <v>516325</v>
-      </c>
-      <c r="R18" t="n">
-        <v>6668756</v>
-      </c>
-      <c r="S18" t="n">
-        <v>5</v>
-      </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>Smedjebacken</t>
-        </is>
-      </c>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>Norrbärke</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>2026-08-09</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>16:58</t>
-        </is>
-      </c>
-      <c r="AA18" t="inlineStr">
-        <is>
-          <t>2026-08-09</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>16:58</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
-        </is>
-      </c>
-      <c r="AD18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT18" t="inlineStr"/>
-      <c r="AW18" t="inlineStr">
-        <is>
-          <t>Alec Bailey</t>
-        </is>
-      </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>Alec Bailey</t>
-        </is>
-      </c>
-      <c r="AY18" t="inlineStr"/>
-      <c r="AZ18" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135775344</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>135775346</v>
-      </c>
-      <c r="B19" t="n">
-        <v>101504</v>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>222498</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Blåsippa</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>Hepatica nobilis</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>Limnäsudden, Dlr</t>
-        </is>
-      </c>
-      <c r="Q19" t="n">
-        <v>516325</v>
-      </c>
-      <c r="R19" t="n">
-        <v>6668729</v>
-      </c>
-      <c r="S19" t="n">
-        <v>5</v>
-      </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="U19" t="inlineStr">
-        <is>
-          <t>Smedjebacken</t>
-        </is>
-      </c>
-      <c r="V19" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>Norrbärke</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>2026-08-09</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>16:59</t>
-        </is>
-      </c>
-      <c r="AA19" t="inlineStr">
-        <is>
-          <t>2026-08-09</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>16:59</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
-        </is>
-      </c>
-      <c r="AD19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT19" t="inlineStr"/>
-      <c r="AW19" t="inlineStr">
-        <is>
-          <t>Alec Bailey</t>
-        </is>
-      </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>Alec Bailey</t>
-        </is>
-      </c>
-      <c r="AY19" t="inlineStr"/>
-      <c r="AZ19" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135775346</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>135775350</v>
-      </c>
-      <c r="B20" t="n">
-        <v>101504</v>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E20" t="n">
-        <v>222498</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Blåsippa</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>Hepatica nobilis</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>Limnäsudden, Dlr</t>
-        </is>
-      </c>
-      <c r="Q20" t="n">
-        <v>516342</v>
-      </c>
-      <c r="R20" t="n">
-        <v>6668692</v>
-      </c>
-      <c r="S20" t="n">
-        <v>5</v>
-      </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="U20" t="inlineStr">
-        <is>
-          <t>Smedjebacken</t>
-        </is>
-      </c>
-      <c r="V20" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>Norrbärke</t>
-        </is>
-      </c>
-      <c r="Y20" t="inlineStr">
-        <is>
-          <t>2026-08-09</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>17:06</t>
-        </is>
-      </c>
-      <c r="AA20" t="inlineStr">
-        <is>
-          <t>2026-08-09</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>17:06</t>
-        </is>
-      </c>
-      <c r="AD20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT20" t="inlineStr"/>
-      <c r="AW20" t="inlineStr">
-        <is>
-          <t>Alec Bailey</t>
-        </is>
-      </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>Alec Bailey</t>
-        </is>
-      </c>
-      <c r="AY20" t="inlineStr"/>
-      <c r="AZ20" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135775350</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>135775354</v>
-      </c>
-      <c r="B21" t="n">
-        <v>101504</v>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E21" t="n">
-        <v>222498</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Blåsippa</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>Hepatica nobilis</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>Limnäsudden, Dlr</t>
-        </is>
-      </c>
-      <c r="Q21" t="n">
-        <v>516349</v>
-      </c>
-      <c r="R21" t="n">
-        <v>6668748</v>
-      </c>
-      <c r="S21" t="n">
-        <v>8</v>
-      </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="U21" t="inlineStr">
-        <is>
-          <t>Smedjebacken</t>
-        </is>
-      </c>
-      <c r="V21" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>Norrbärke</t>
-        </is>
-      </c>
-      <c r="Y21" t="inlineStr">
-        <is>
-          <t>2026-08-09</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>17:21</t>
-        </is>
-      </c>
-      <c r="AA21" t="inlineStr">
-        <is>
-          <t>2026-08-09</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>17:21</t>
-        </is>
-      </c>
-      <c r="AD21" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE21" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG21" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT21" t="inlineStr"/>
-      <c r="AW21" t="inlineStr">
-        <is>
-          <t>Alec Bailey</t>
-        </is>
-      </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>Alec Bailey</t>
-        </is>
-      </c>
-      <c r="AY21" t="inlineStr"/>
-      <c r="AZ21" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135775354</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>135775355</v>
-      </c>
-      <c r="B22" t="n">
-        <v>99100</v>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E22" t="n">
-        <v>223049</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Ormbär</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>Paris quadrifolia</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>Limnäsudden, Dlr</t>
-        </is>
-      </c>
-      <c r="Q22" t="n">
-        <v>516339</v>
-      </c>
-      <c r="R22" t="n">
-        <v>6668746</v>
-      </c>
-      <c r="S22" t="n">
-        <v>12</v>
-      </c>
-      <c r="T22" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="U22" t="inlineStr">
-        <is>
-          <t>Smedjebacken</t>
-        </is>
-      </c>
-      <c r="V22" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>Norrbärke</t>
-        </is>
-      </c>
-      <c r="Y22" t="inlineStr">
-        <is>
-          <t>2026-08-09</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>17:24</t>
-        </is>
-      </c>
-      <c r="AA22" t="inlineStr">
-        <is>
-          <t>2026-08-09</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>17:24</t>
-        </is>
-      </c>
-      <c r="AD22" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE22" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG22" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT22" t="inlineStr"/>
-      <c r="AW22" t="inlineStr">
-        <is>
-          <t>Alec Bailey</t>
-        </is>
-      </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>Alec Bailey</t>
-        </is>
-      </c>
-      <c r="AY22" t="inlineStr"/>
-      <c r="AZ22" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135775355</t>
         </is>
       </c>
     </row>
@@ -3175,15 +2152,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 54940-2025 artfynd.xlsx
+++ b/artfynd/A 54940-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ13"/>
+  <dimension ref="A1:AZ22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -811,10 +811,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>96603593</v>
+        <v>135775340</v>
       </c>
       <c r="B3" t="n">
-        <v>91680</v>
+        <v>96507</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -822,37 +822,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3215</v>
+        <v>2812</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Limnäsudden - Skarvikberget, Dlr</t>
+          <t>Limnäsudden, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>516225</v>
+        <v>516356</v>
       </c>
       <c r="R3" t="n">
-        <v>6668675</v>
+        <v>6668771</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -879,12 +876,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2021-10-11</t>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2021-10-11</t>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -893,44 +900,33 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>kalkmarksskog</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96603593</t>
+          <t>https://artportalen.se/Sighting/135775340</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>96603589</v>
+        <v>96603593</v>
       </c>
       <c r="B4" t="n">
-        <v>92869</v>
+        <v>91680</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -938,21 +934,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4769</v>
+        <v>3215</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -1037,13 +1033,13 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96603589</t>
+          <t>https://artportalen.se/Sighting/96603593</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129974173</v>
+        <v>96603589</v>
       </c>
       <c r="B5" t="n">
         <v>92869</v>
@@ -1077,14 +1073,14 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Skarviksberget, Dlr</t>
+          <t>Limnäsudden - Skarvikberget, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>516220</v>
+        <v>516225</v>
       </c>
       <c r="R5" t="n">
-        <v>6668664</v>
+        <v>6668675</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1111,12 +1107,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2021-10-11</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2021-10-11</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1131,27 +1127,12 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>Lågörtgranskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Inslag av gamla tallar. Kalkmarksskog. Avverkningsplanerat.</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+          <t>kalkmarksskog</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1168,16 +1149,16 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129974173</t>
+          <t>https://artportalen.se/Sighting/96603589</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129974143</v>
+        <v>129974173</v>
       </c>
       <c r="B6" t="n">
-        <v>91282</v>
+        <v>92869</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1185,21 +1166,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5685</v>
+        <v>4769</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1212,10 +1193,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>516272</v>
+        <v>516220</v>
       </c>
       <c r="R6" t="n">
-        <v>6668613</v>
+        <v>6668664</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1272,17 +1253,17 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>tallåga bland gamla granlågor # Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1299,52 +1280,43 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129974143</t>
+          <t>https://artportalen.se/Sighting/129974173</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129974179</v>
+        <v>129974143</v>
       </c>
       <c r="B7" t="n">
-        <v>99118</v>
+        <v>91282</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>5685</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Fr.) Jülich</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1352,10 +1324,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>516259</v>
+        <v>516272</v>
       </c>
       <c r="R7" t="n">
-        <v>6668701</v>
+        <v>6668613</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1410,6 +1382,21 @@
           <t>Inslag av gamla tallar. Kalkmarksskog. Avverkningsplanerat.</t>
         </is>
       </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>tallåga bland gamla granlågor # Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
@@ -1424,63 +1411,51 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129974179</t>
+          <t>https://artportalen.se/Sighting/129974143</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129974211</v>
+        <v>135775349</v>
       </c>
       <c r="B8" t="n">
-        <v>99118</v>
+        <v>4777</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>100299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Skarviksberget, Dlr</t>
+          <t>Limnäsudden, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>516279</v>
+        <v>516333</v>
       </c>
       <c r="R8" t="n">
-        <v>6668684</v>
+        <v>6668702</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1507,12 +1482,27 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>17:05</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Stående död gran, lågörtgranskog</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1521,83 +1511,80 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>Lågörtgranskog</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>Inslag av gamla tallar. Kalkmarksskog. Avverkningsplanerat.</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129974211</t>
+          <t>https://artportalen.se/Sighting/135775349</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>96603576</v>
+        <v>129974179</v>
       </c>
       <c r="B9" t="n">
-        <v>101326</v>
+        <v>99118</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Limnäsudden - Skarvikberget, Dlr</t>
+          <t>Skarviksberget, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>516225</v>
+        <v>516259</v>
       </c>
       <c r="R9" t="n">
-        <v>6668675</v>
+        <v>6668701</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1624,12 +1611,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2021-10-11</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2021-10-11</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1644,12 +1631,12 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Lågörtgranskog</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>kalkmarksskog</t>
+          <t>Inslag av gamla tallar. Kalkmarksskog. Avverkningsplanerat.</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1666,42 +1653,50 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96603576</t>
+          <t>https://artportalen.se/Sighting/129974179</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129974105</v>
+        <v>129974211</v>
       </c>
       <c r="B10" t="n">
-        <v>101325</v>
+        <v>99118</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
@@ -1711,13 +1706,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>516331</v>
+        <v>516279</v>
       </c>
       <c r="R10" t="n">
-        <v>6668692</v>
+        <v>6668684</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1766,7 +1761,7 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>inslag av gamla tallar</t>
+          <t>Inslag av gamla tallar. Kalkmarksskog. Avverkningsplanerat.</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1783,16 +1778,16 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129974105</t>
+          <t>https://artportalen.se/Sighting/129974211</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129974151</v>
+        <v>96603576</v>
       </c>
       <c r="B11" t="n">
-        <v>101325</v>
+        <v>101326</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1824,14 +1819,14 @@
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Skarviksberget, Dlr</t>
+          <t>Limnäsudden - Skarvikberget, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>516214</v>
+        <v>516225</v>
       </c>
       <c r="R11" t="n">
-        <v>6668657</v>
+        <v>6668675</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1858,12 +1853,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2021-10-11</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2021-10-11</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1878,12 +1873,12 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>Lågörtgranskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Inslag av gamla tallar. Kalkmarksskog. Avverkningsplanerat.</t>
+          <t>kalkmarksskog</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1900,13 +1895,13 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129974151</t>
+          <t>https://artportalen.se/Sighting/96603576</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129974181</v>
+        <v>129974105</v>
       </c>
       <c r="B12" t="n">
         <v>101325</v>
@@ -1945,13 +1940,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>516284</v>
+        <v>516331</v>
       </c>
       <c r="R12" t="n">
-        <v>6668713</v>
+        <v>6668692</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2000,7 +1995,7 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Inslag av gamla tallar. Kalkmarksskog. Avverkningsplanerat.</t>
+          <t>inslag av gamla tallar</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2017,13 +2012,13 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129974181</t>
+          <t>https://artportalen.se/Sighting/129974105</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129974196</v>
+        <v>129974151</v>
       </c>
       <c r="B13" t="n">
         <v>101325</v>
@@ -2062,10 +2057,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>516330</v>
+        <v>516214</v>
       </c>
       <c r="R13" t="n">
-        <v>6668614</v>
+        <v>6668657</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2134,7 +2129,1035 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/129974151</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>129974181</v>
+      </c>
+      <c r="B14" t="n">
+        <v>101325</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Skarviksberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>516284</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6668713</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Norrbärke</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>Inslag av gamla tallar. Kalkmarksskog. Avverkningsplanerat.</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129974181</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>129974196</v>
+      </c>
+      <c r="B15" t="n">
+        <v>101325</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Skarviksberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>516330</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6668614</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Norrbärke</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>Inslag av gamla tallar. Kalkmarksskog. Avverkningsplanerat.</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/129974196</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>135775337</v>
+      </c>
+      <c r="B16" t="n">
+        <v>101505</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Limnäsudden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>516387</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6668808</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Norrbärke</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>16:50</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>16:50</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135775337</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>135775341</v>
+      </c>
+      <c r="B17" t="n">
+        <v>101505</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Limnäsudden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>516353</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6668765</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Norrbärke</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>16:54</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>16:54</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135775341</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>135775344</v>
+      </c>
+      <c r="B18" t="n">
+        <v>101505</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Limnäsudden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>516325</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6668756</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Norrbärke</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>16:58</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>16:58</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135775344</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>135775346</v>
+      </c>
+      <c r="B19" t="n">
+        <v>101505</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Limnäsudden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>516325</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6668729</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Norrbärke</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>16:59</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>16:59</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135775346</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>135775350</v>
+      </c>
+      <c r="B20" t="n">
+        <v>101505</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Limnäsudden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>516342</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6668692</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Norrbärke</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>17:06</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>17:06</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135775350</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>135775354</v>
+      </c>
+      <c r="B21" t="n">
+        <v>101505</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Limnäsudden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>516349</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6668748</v>
+      </c>
+      <c r="S21" t="n">
+        <v>8</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Norrbärke</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135775354</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>135775355</v>
+      </c>
+      <c r="B22" t="n">
+        <v>99101</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>223049</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Ormbär</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Paris quadrifolia</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Limnäsudden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>516339</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6668746</v>
+      </c>
+      <c r="S22" t="n">
+        <v>12</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Norrbärke</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>17:24</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>17:24</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135775355</t>
         </is>
       </c>
     </row>
@@ -2152,6 +3175,15 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 54940-2025 artfynd.xlsx
+++ b/artfynd/A 54940-2025 artfynd.xlsx
@@ -814,7 +814,7 @@
         <v>135775340</v>
       </c>
       <c r="B3" t="n">
-        <v>96507</v>
+        <v>96508</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -2372,7 +2372,7 @@
         <v>135775337</v>
       </c>
       <c r="B16" t="n">
-        <v>101505</v>
+        <v>101506</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2484,7 +2484,7 @@
         <v>135775341</v>
       </c>
       <c r="B17" t="n">
-        <v>101505</v>
+        <v>101506</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2596,7 +2596,7 @@
         <v>135775344</v>
       </c>
       <c r="B18" t="n">
-        <v>101505</v>
+        <v>101506</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2713,7 +2713,7 @@
         <v>135775346</v>
       </c>
       <c r="B19" t="n">
-        <v>101505</v>
+        <v>101506</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2830,7 +2830,7 @@
         <v>135775350</v>
       </c>
       <c r="B20" t="n">
-        <v>101505</v>
+        <v>101506</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2942,7 +2942,7 @@
         <v>135775354</v>
       </c>
       <c r="B21" t="n">
-        <v>101505</v>
+        <v>101506</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3054,7 +3054,7 @@
         <v>135775355</v>
       </c>
       <c r="B22" t="n">
-        <v>99101</v>
+        <v>99102</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 54940-2025 artfynd.xlsx
+++ b/artfynd/A 54940-2025 artfynd.xlsx
@@ -814,7 +814,7 @@
         <v>135775340</v>
       </c>
       <c r="B3" t="n">
-        <v>96508</v>
+        <v>96514</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -2372,7 +2372,7 @@
         <v>135775337</v>
       </c>
       <c r="B16" t="n">
-        <v>101506</v>
+        <v>101512</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2484,7 +2484,7 @@
         <v>135775341</v>
       </c>
       <c r="B17" t="n">
-        <v>101506</v>
+        <v>101512</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2596,7 +2596,7 @@
         <v>135775344</v>
       </c>
       <c r="B18" t="n">
-        <v>101506</v>
+        <v>101512</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2713,7 +2713,7 @@
         <v>135775346</v>
       </c>
       <c r="B19" t="n">
-        <v>101506</v>
+        <v>101512</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2830,7 +2830,7 @@
         <v>135775350</v>
       </c>
       <c r="B20" t="n">
-        <v>101506</v>
+        <v>101512</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2942,7 +2942,7 @@
         <v>135775354</v>
       </c>
       <c r="B21" t="n">
-        <v>101506</v>
+        <v>101512</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3054,7 +3054,7 @@
         <v>135775355</v>
       </c>
       <c r="B22" t="n">
-        <v>99102</v>
+        <v>99108</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 54940-2025 artfynd.xlsx
+++ b/artfynd/A 54940-2025 artfynd.xlsx
@@ -814,7 +814,7 @@
         <v>135775340</v>
       </c>
       <c r="B3" t="n">
-        <v>96514</v>
+        <v>96515</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -2372,7 +2372,7 @@
         <v>135775337</v>
       </c>
       <c r="B16" t="n">
-        <v>101512</v>
+        <v>101513</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2484,7 +2484,7 @@
         <v>135775341</v>
       </c>
       <c r="B17" t="n">
-        <v>101512</v>
+        <v>101513</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2596,7 +2596,7 @@
         <v>135775344</v>
       </c>
       <c r="B18" t="n">
-        <v>101512</v>
+        <v>101513</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2713,7 +2713,7 @@
         <v>135775346</v>
       </c>
       <c r="B19" t="n">
-        <v>101512</v>
+        <v>101513</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2830,7 +2830,7 @@
         <v>135775350</v>
       </c>
       <c r="B20" t="n">
-        <v>101512</v>
+        <v>101513</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2942,7 +2942,7 @@
         <v>135775354</v>
       </c>
       <c r="B21" t="n">
-        <v>101512</v>
+        <v>101513</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3054,7 +3054,7 @@
         <v>135775355</v>
       </c>
       <c r="B22" t="n">
-        <v>99108</v>
+        <v>99109</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
